--- a/resources/templates/standard/L1100-11.xlsx
+++ b/resources/templates/standard/L1100-11.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>NO</t>
   </si>
@@ -1025,7 +1028,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -1113,22 +1118,22 @@
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G4" s="16"/>
       <c r="H4" s="16"/>
@@ -1142,7 +1147,7 @@
       <c r="P4" s="18"/>
       <c r="Q4" s="16"/>
       <c r="R4" s="19" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S4" s="7"/>
       <c r="T4" s="7"/>
@@ -1160,43 +1165,43 @@
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
       <c r="E5" s="20" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K5" s="21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L5" s="21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M5" s="21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N5" s="21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O5" s="21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P5" s="21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q5" s="21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R5" s="19"/>
       <c r="S5" s="7"/>
@@ -1215,7 +1220,7 @@
       <c r="C6" s="23"/>
       <c r="D6" s="23"/>
       <c r="E6" s="24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F6" s="25"/>
       <c r="G6" s="25"/>
@@ -1246,7 +1251,7 @@
       <c r="C7" s="23"/>
       <c r="D7" s="23"/>
       <c r="E7" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F7" s="28"/>
       <c r="G7" s="28"/>
@@ -1306,7 +1311,7 @@
       <c r="C9" s="33"/>
       <c r="D9" s="33"/>
       <c r="E9" s="27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
@@ -1337,7 +1342,7 @@
       <c r="C10" s="33"/>
       <c r="D10" s="33"/>
       <c r="E10" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F10" s="28"/>
       <c r="G10" s="28"/>
@@ -1397,7 +1402,7 @@
       <c r="C12" s="33"/>
       <c r="D12" s="33"/>
       <c r="E12" s="27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F12" s="28"/>
       <c r="G12" s="28"/>
@@ -1428,7 +1433,7 @@
       <c r="C13" s="33"/>
       <c r="D13" s="33"/>
       <c r="E13" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F13" s="28"/>
       <c r="G13" s="28"/>
@@ -1488,7 +1493,7 @@
       <c r="C15" s="33"/>
       <c r="D15" s="38"/>
       <c r="E15" s="27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="34"/>
@@ -1519,7 +1524,7 @@
       <c r="C16" s="33"/>
       <c r="D16" s="38"/>
       <c r="E16" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F16" s="28"/>
       <c r="G16" s="28"/>
@@ -1579,7 +1584,7 @@
       <c r="C18" s="33"/>
       <c r="D18" s="38"/>
       <c r="E18" s="27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F18" s="28"/>
       <c r="G18" s="28"/>
@@ -1610,7 +1615,7 @@
       <c r="C19" s="33"/>
       <c r="D19" s="38"/>
       <c r="E19" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F19" s="28"/>
       <c r="G19" s="28"/>
@@ -1670,7 +1675,7 @@
       <c r="C21" s="33"/>
       <c r="D21" s="38"/>
       <c r="E21" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F21" s="42"/>
       <c r="G21" s="34"/>
@@ -1701,7 +1706,7 @@
       <c r="C22" s="33"/>
       <c r="D22" s="38"/>
       <c r="E22" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F22" s="43"/>
       <c r="G22" s="43"/>
@@ -1761,7 +1766,7 @@
       <c r="C24" s="33"/>
       <c r="D24" s="38"/>
       <c r="E24" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F24" s="42"/>
       <c r="G24" s="34"/>
@@ -1792,7 +1797,7 @@
       <c r="C25" s="33"/>
       <c r="D25" s="38"/>
       <c r="E25" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F25" s="43"/>
       <c r="G25" s="43"/>
@@ -1852,7 +1857,7 @@
       <c r="C27" s="33"/>
       <c r="D27" s="38"/>
       <c r="E27" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F27" s="42"/>
       <c r="G27" s="34"/>
@@ -1883,7 +1888,7 @@
       <c r="C28" s="33"/>
       <c r="D28" s="38"/>
       <c r="E28" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F28" s="43"/>
       <c r="G28" s="43"/>
@@ -1943,7 +1948,7 @@
       <c r="C30" s="33"/>
       <c r="D30" s="33"/>
       <c r="E30" s="27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F30" s="34"/>
       <c r="G30" s="34"/>
@@ -1974,7 +1979,7 @@
       <c r="C31" s="33"/>
       <c r="D31" s="33"/>
       <c r="E31" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F31" s="28"/>
       <c r="G31" s="28"/>
@@ -2034,7 +2039,7 @@
       <c r="C33" s="33"/>
       <c r="D33" s="38"/>
       <c r="E33" s="27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F33" s="43"/>
       <c r="G33" s="28"/>
@@ -2065,7 +2070,7 @@
       <c r="C34" s="33"/>
       <c r="D34" s="38"/>
       <c r="E34" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F34" s="43"/>
       <c r="G34" s="43"/>
@@ -2143,19 +2148,19 @@
       <c r="U36" s="48"/>
       <c r="V36" s="48"/>
       <c r="W36" s="49" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X36" s="50" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y36" s="50" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z36" s="50" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA36" s="50" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.25">
